--- a/education_forms/047_online_mcq_assessment--education_forms.xlsx
+++ b/education_forms/047_online_mcq_assessment--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>question_1_label</t>
+          <t>question_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>What is your name</t>
+          <t>What is your age?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>question_2_label</t>
+          <t>question_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>What is your age</t>
+          <t>What is your educational background?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>question_3_label</t>
+          <t>question_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>What is your email</t>
+          <t>How would you rate your computer skills?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>question_4_label</t>
+          <t>question_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What is your phone number</t>
+          <t>What is your primary language spoken at home?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,24 +607,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>question_5_label</t>
+          <t>question_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>What is your date of birth</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+          <t>How many hours do you spend online daily?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -634,24 +630,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>question_6_label</t>
+          <t>question_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>What is your time of birth</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+          <t>What is your preferred time of day for online activities?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -661,24 +653,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>question_7_label</t>
+          <t>question_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>What is your note</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+          <t>Do you agree or disagree with the following statement?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -688,40 +676,40 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>question_8_label</t>
+          <t>question_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What is your select one</t>
+          <t>What is your preferred mode of communication for online interactions?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>question_9_label</t>
+          <t>question_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>What is your select multiple</t>
+          <t>How would you rate your experience with online learning platforms?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -734,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>question_10_label</t>
+          <t>question_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>What is your multiple date</t>
+          <t>What is your level of satisfaction with the current online learning platform?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -757,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>question_11_label</t>
+          <t>question_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>What is your multiple time</t>
+          <t>How often do you use online resources for learning?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -780,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>question_12_label</t>
+          <t>question_12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>What is your multiple date</t>
+          <t>How would you rate your ability to find relevant online content?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -808,292 +796,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>question_13_label</t>
+          <t>question_13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>What is your multiple select one</t>
+          <t>What is your preferred device for online activities?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>question_14_label</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>What is your multiple select multiple</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>question_15_label</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>What is your multiple select multiple</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>question_16_label</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>What is your select multiple</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>question_17_label</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>What is your date</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>question_18_label</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>What is your time</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>question_19_label</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>What is your date</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>question_20_label</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>What is your time</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>question_21_label</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>What is your select one</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>question_22_label</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>What is your select one</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>question_23_label</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>What is your select multiple</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>question_24_label</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>What is your select multiple</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>question_25_label</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>What is your time</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1110,12 +822,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1138,374 +850,731 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>question_8_label_choices</t>
+          <t>question_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>a._18-24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>a. 18-24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>question_8_label_choices</t>
+          <t>question_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>b._25-34</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>b. 25-34</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>question_8_label_choices</t>
+          <t>question_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>c._35-44</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>c. 35-44</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>question_9_label_choices</t>
+          <t>question_1_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>d._45-54</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>d. 45-54</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>question_9_label_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>a._high_school</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>a. High school</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>question_13_label_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>b._bachelor's_degree</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>b. Bachelor's degree</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>question_13_label_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>c._master's_degree</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>c. Master's degree</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>question_14_label_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>d._doctoral_degree</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>d. Doctoral degree</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>question_14_label_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>a._beginner</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>a. Beginner</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>question_15_label_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>b._intermediate</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>b. Intermediate</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>question_15_label_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>c._advanced</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>c. Advanced</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>question_16_label_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>a._english</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>a. English</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>question_16_label_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>b._other_(please_specify)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>b. Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>question_21_label_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>a._morning</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>a. Morning</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>question_21_label_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>b._afternoon</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>b. Afternoon</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>question_21_label_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>c._evening</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>c. Evening</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>question_22_label_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>d._anytime</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>d. Anytime</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>question_22_label_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>a._yes</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>a. Yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>question_23_label_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>b._no</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>b. No</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>question_23_label_choices</t>
+          <t>question_8_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>a._email</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>a. Email</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>question_24_label_choices</t>
+          <t>question_8_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>b._phone_call</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>b. Phone call</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>question_24_label_choices</t>
+          <t>question_8_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>c._video_call</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>c. Video call</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>question_8_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>d._social_media</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>d. Social media</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>question_9_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>a._very_good</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>a. Very good</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>question_9_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>b._good</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>b. Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>question_9_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>c._average</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>c. Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>question_9_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>d._poor</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>d. Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>question_10_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>a._very_satisfied</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>a. Very satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>question_10_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>b._satisfied</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>b. Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>question_10_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>c._neutral</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>c. Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>question_10_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>d._dissatisfied</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>d. Dissatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>question_11_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>a._frequently</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>a. Frequently</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>question_11_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>b._occasionally</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>b. Occasionally</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>question_11_choices</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>c._rarely</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>c. Rarely</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>question_11_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>d._never</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>d. Never</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>question_12_choices</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>a._very_good</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>a. Very good</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>question_12_choices</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>b._good</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>b. Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>question_12_choices</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>c._average</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>c. Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>question_12_choices</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>d._poor</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>d. Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>question_13_choices</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>a._laptop</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>a. Laptop</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>question_13_choices</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>b._smartphone</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>b. Smartphone</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>question_13_choices</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>c._tablet</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>c. Tablet</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>question_13_choices</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>d._other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>d. Other (please specify)</t>
         </is>
       </c>
     </row>
